--- a/Excel/JingLingConfig.xlsx
+++ b/Excel/JingLingConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8773E043-1041-4232-88EE-3AEBF16C5565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E6C988-7231-4FBE-860A-14FAEE9E4E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JingLingProto" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -68,7 +68,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{AAD6C0D3-924B-481D-AED4-55A29C94E229}">
+    <comment ref="U3" authorId="0" shapeId="0" xr:uid="{AAD6C0D3-924B-481D-AED4-55A29C94E229}">
       <text>
         <r>
           <rPr>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="152">
   <si>
     <t>Id</t>
   </si>
@@ -435,6 +435,171 @@
   </si>
   <si>
     <t>200103;0.05</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lucky Star</t>
+  </si>
+  <si>
+    <t>Raccoon Spirit</t>
+  </si>
+  <si>
+    <t>Greedy Turtle</t>
+  </si>
+  <si>
+    <t>Fish Spirit</t>
+  </si>
+  <si>
+    <t>Jaguar</t>
+  </si>
+  <si>
+    <t>Barbie Knot</t>
+  </si>
+  <si>
+    <t>Flame Magic</t>
+  </si>
+  <si>
+    <t>Alchemy Vitality Potion</t>
+  </si>
+  <si>
+    <t>Ghost</t>
+  </si>
+  <si>
+    <t>Naughty Spirit</t>
+  </si>
+  <si>
+    <t>Bobo</t>
+  </si>
+  <si>
+    <t>Hua Hua</t>
+  </si>
+  <si>
+    <t>Dazed</t>
+  </si>
+  <si>
+    <t>The Pumpkin Villain</t>
+  </si>
+  <si>
+    <t>Name_EN</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bear Baby</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProDes_EN</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack power increases by 50 points</t>
+  </si>
+  <si>
+    <t>Life cap + 500 points</t>
+  </si>
+  <si>
+    <t>Critical Hit Rate + 1%</t>
+  </si>
+  <si>
+    <t>Life cap + 1%</t>
+  </si>
+  <si>
+    <t>Hit level increased by 50 points</t>
+  </si>
+  <si>
+    <t>Damage bonus +5%</t>
+  </si>
+  <si>
+    <t>Increased chance of evading attacks by 1%</t>
+  </si>
+  <si>
+    <t>Spell strength is increased by 100 points.</t>
+  </si>
+  <si>
+    <t>Attack +100</t>
+  </si>
+  <si>
+    <t>Life limit + 1000 points</t>
+  </si>
+  <si>
+    <t>Attack strength increased by 100 points</t>
+  </si>
+  <si>
+    <t>Anti-burst rate +1%</t>
+  </si>
+  <si>
+    <t>Defense Enhancement 100 points</t>
+  </si>
+  <si>
+    <t>Critical hit probability + 5%</t>
+  </si>
+  <si>
+    <t>Every day, we will randomly give you some gold coins!</t>
+  </si>
+  <si>
+    <t>Help players actively pick up the gold coins on the ground</t>
+  </si>
+  <si>
+    <t>Help players actively pick up the gold coins and items on the ground</t>
+  </si>
+  <si>
+    <t>Each time a player is injured during a battle, there is a certain probability of releasing their healing ability to restore a certain amount of health.</t>
+  </si>
+  <si>
+    <t>The number of gold coins obtained from enemies has increased by 5%</t>
+  </si>
+  <si>
+    <t>Help players actively pick up gold coins and items on the ground. It can open your inventory at any location in the world.</t>
+  </si>
+  <si>
+    <t>Each time the player enters combat, a defense state is applied, reducing damage taken by 5% for 30 seconds.</t>
+  </si>
+  <si>
+    <t>When the player is attacked by enemies, a random magic attack will hit the enemy</t>
+  </si>
+  <si>
+    <t>Each time a player enters a battle, an attack state will be released, increasing the attack by 5% for 30 seconds.</t>
+  </si>
+  <si>
+    <t>When the player's health drops to 30%, a range skill will be released around the player, causing 2-second stun</t>
+  </si>
+  <si>
+    <t>There is a chance each time a skill is used to release an additional shockwave skill forward.</t>
+  </si>
+  <si>
+    <t>Always find some colorless crystals on the enemies</t>
+  </si>
+  <si>
+    <t>Can start refining your brand-new equipment at any location in the world</t>
+  </si>
+  <si>
+    <t>Each time the player is attacked and takes damage, there is a probability that a range skill will be released nearby, causing damage.</t>
+  </si>
+  <si>
+    <t>Help players actively pick up the gold coins and items on the ground. Every time a player enters a battle, there is a probability to summon one of their clones to assist them in the fight.</t>
+  </si>
+  <si>
+    <t>Des_EN</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Encountered randomly in the wild</t>
+  </si>
+  <si>
+    <t>Points system acquisition</t>
+  </si>
+  <si>
+    <t>Has a chance to be encountered in the wild</t>
+  </si>
+  <si>
+    <t>Obtained through the Sign-in System</t>
+  </si>
+  <si>
+    <t>GetDes_EN</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -892,34 +1057,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:S28"/>
+  <dimension ref="C1:W28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.125" style="2" customWidth="1"/>
-    <col min="5" max="6" width="14.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="18.75" style="2" customWidth="1"/>
-    <col min="12" max="12" width="62.25" style="2" customWidth="1"/>
-    <col min="13" max="15" width="9" style="2"/>
-    <col min="16" max="16" width="18.75" style="2" customWidth="1"/>
-    <col min="17" max="17" width="15.5" style="2" customWidth="1"/>
-    <col min="18" max="19" width="18.75" style="2" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="2"/>
+    <col min="4" max="5" width="15.125" style="2" customWidth="1"/>
+    <col min="6" max="7" width="14.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="23.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="11.5" style="2" customWidth="1"/>
+    <col min="12" max="13" width="18.75" style="2" customWidth="1"/>
+    <col min="14" max="15" width="62.25" style="2" customWidth="1"/>
+    <col min="16" max="18" width="9" style="2"/>
+    <col min="19" max="20" width="18.75" style="2" customWidth="1"/>
+    <col min="21" max="21" width="15.5" style="2" customWidth="1"/>
+    <col min="22" max="23" width="18.75" style="2" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S2" s="2" t="s">
+    <row r="1" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="W2" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -927,52 +1104,64 @@
         <v>1</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="O3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="T3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="V3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="W3" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -980,52 +1169,64 @@
         <v>12</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="O4" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="P4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="T4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="U4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="V4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="W4" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>24</v>
       </c>
@@ -1033,10 +1234,10 @@
         <v>25</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>25</v>
@@ -1045,842 +1246,1034 @@
         <v>25</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="M5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="Q5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="R5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="S5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="T5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="U5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R5" s="3" t="s">
+      <c r="V5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="W5" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="3:19" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="3:23" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="4">
         <v>10001</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="4">
-        <v>10001</v>
+      <c r="E6" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="F6" s="4">
         <v>10001</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="4">
+        <v>10001</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="4">
+      <c r="I6" s="4">
         <v>10001</v>
       </c>
-      <c r="I6" s="4">
+      <c r="J6" s="4">
         <v>10</v>
       </c>
-      <c r="J6" s="4">
+      <c r="K6" s="4">
         <v>-1</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="M6" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="N6" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="M6" s="4">
+      <c r="O6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="P6" s="4">
         <v>2</v>
       </c>
-      <c r="N6" s="4">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4">
-        <v>0</v>
-      </c>
-      <c r="P6" s="6" t="s">
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
+        <v>0</v>
+      </c>
+      <c r="S6" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="T6" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="U6" s="4">
         <v>1</v>
       </c>
-      <c r="R6" s="4">
+      <c r="V6" s="4">
         <v>60400501</v>
       </c>
-      <c r="S6" s="4">
+      <c r="W6" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="4">
         <v>10002</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="4">
-        <v>10002</v>
+      <c r="E7" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="F7" s="4">
         <v>10002</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="4">
+        <v>10002</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="4">
+      <c r="I7" s="4">
         <v>10002</v>
       </c>
-      <c r="I7" s="4">
+      <c r="J7" s="4">
         <v>8</v>
       </c>
-      <c r="J7" s="4">
+      <c r="K7" s="4">
         <v>-1</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="L7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="M7" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="N7" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="M7" s="4">
+      <c r="O7" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="P7" s="4">
         <v>2</v>
       </c>
-      <c r="N7" s="4">
-        <v>0</v>
-      </c>
-      <c r="O7" s="4">
-        <v>0</v>
-      </c>
-      <c r="P7" s="6" t="s">
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4">
+        <v>0</v>
+      </c>
+      <c r="S7" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="Q7" s="4">
+      <c r="T7" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="U7" s="4">
         <v>2</v>
       </c>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4">
+      <c r="V7" s="4"/>
+      <c r="W7" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="4">
         <v>10003</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="4">
-        <v>10003</v>
+      <c r="E8" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="F8" s="4">
         <v>10003</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="4">
+        <v>10003</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="4">
+      <c r="I8" s="4">
         <v>10008</v>
       </c>
-      <c r="I8" s="4">
+      <c r="J8" s="4">
         <v>10</v>
       </c>
-      <c r="J8" s="4">
+      <c r="K8" s="4">
         <v>-1</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="L8" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="M8" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="N8" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="M8" s="4">
+      <c r="O8" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="P8" s="4">
         <v>2</v>
       </c>
-      <c r="N8" s="4">
-        <v>0</v>
-      </c>
-      <c r="O8" s="4">
-        <v>0</v>
-      </c>
-      <c r="P8" s="6" t="s">
+      <c r="Q8" s="4">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4">
+        <v>0</v>
+      </c>
+      <c r="S8" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="Q8" s="4">
-        <v>0</v>
-      </c>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4">
+      <c r="T8" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="U8" s="4">
+        <v>0</v>
+      </c>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="4">
         <v>10004</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="4">
-        <v>10004</v>
+      <c r="E9" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="F9" s="4">
         <v>10004</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="4">
+        <v>10004</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="H9" s="4">
+      <c r="I9" s="4">
         <v>10004</v>
       </c>
-      <c r="I9" s="4">
+      <c r="J9" s="4">
         <v>10</v>
       </c>
-      <c r="J9" s="4">
+      <c r="K9" s="4">
         <v>-1</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="L9" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="M9" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="N9" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="M9" s="4">
+      <c r="O9" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="P9" s="4">
         <v>2</v>
       </c>
-      <c r="N9" s="4">
-        <v>0</v>
-      </c>
-      <c r="O9" s="4">
-        <v>0</v>
-      </c>
-      <c r="P9" s="6" t="s">
+      <c r="Q9" s="4">
+        <v>0</v>
+      </c>
+      <c r="R9" s="4">
+        <v>0</v>
+      </c>
+      <c r="S9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="Q9" s="4">
+      <c r="T9" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="U9" s="4">
         <v>4</v>
       </c>
-      <c r="R9" s="4">
+      <c r="V9" s="4">
         <v>64100001</v>
       </c>
-      <c r="S9" s="4">
+      <c r="W9" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="4">
         <v>10005</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="4">
-        <v>10005</v>
+      <c r="E10" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="F10" s="4">
         <v>10005</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="4">
+        <v>10005</v>
+      </c>
+      <c r="H10" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H10" s="4">
+      <c r="I10" s="4">
         <v>10016</v>
       </c>
-      <c r="I10" s="4">
+      <c r="J10" s="4">
         <v>10</v>
       </c>
-      <c r="J10" s="4">
+      <c r="K10" s="4">
         <v>-1</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="L10" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="M10" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="N10" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="M10" s="4">
+      <c r="O10" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="P10" s="4">
         <v>2</v>
       </c>
-      <c r="N10" s="4">
-        <v>0</v>
-      </c>
-      <c r="O10" s="4">
-        <v>0</v>
-      </c>
-      <c r="P10" s="6" t="s">
+      <c r="Q10" s="4">
+        <v>0</v>
+      </c>
+      <c r="R10" s="4">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="Q10" s="4">
+      <c r="T10" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="U10" s="4">
         <v>5</v>
       </c>
-      <c r="R10" s="4" t="s">
+      <c r="V10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="S10" s="4">
+      <c r="W10" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="4">
         <v>10006</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="4">
-        <v>10006</v>
+      <c r="E11" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="F11" s="4">
         <v>10006</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="4">
+        <v>10006</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="H11" s="4">
+      <c r="I11" s="4">
         <v>10005</v>
       </c>
-      <c r="I11" s="4">
+      <c r="J11" s="4">
         <v>20</v>
       </c>
-      <c r="J11" s="4">
+      <c r="K11" s="4">
         <v>-1</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="L11" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="M11" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="N11" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="M11" s="4">
+      <c r="O11" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="P11" s="4">
         <v>2</v>
       </c>
-      <c r="N11" s="4">
-        <v>0</v>
-      </c>
-      <c r="O11" s="4">
-        <v>0</v>
-      </c>
-      <c r="P11" s="6" t="s">
+      <c r="Q11" s="4">
+        <v>0</v>
+      </c>
+      <c r="R11" s="4">
+        <v>0</v>
+      </c>
+      <c r="S11" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="Q11" s="4">
+      <c r="T11" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="U11" s="4">
         <v>7</v>
       </c>
-      <c r="R11" s="4">
+      <c r="V11" s="4">
         <v>1004</v>
       </c>
-      <c r="S11" s="4">
+      <c r="W11" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="4">
         <v>10007</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="4">
-        <v>10007</v>
+      <c r="E12" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="F12" s="4">
         <v>10007</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="4">
+        <v>10007</v>
+      </c>
+      <c r="H12" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="H12" s="4">
+      <c r="I12" s="4">
         <v>10006</v>
       </c>
-      <c r="I12" s="4">
+      <c r="J12" s="4">
         <v>11</v>
       </c>
-      <c r="J12" s="4">
+      <c r="K12" s="4">
         <v>-1</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="L12" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="M12" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="N12" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="M12" s="4">
+      <c r="O12" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="P12" s="4">
         <v>2</v>
       </c>
-      <c r="N12" s="4">
-        <v>0</v>
-      </c>
-      <c r="O12" s="4">
-        <v>0</v>
-      </c>
-      <c r="P12" s="6" t="s">
+      <c r="Q12" s="4">
+        <v>0</v>
+      </c>
+      <c r="R12" s="4">
+        <v>0</v>
+      </c>
+      <c r="S12" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="T12" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="U12" s="4">
         <v>4</v>
       </c>
-      <c r="R12" s="4">
+      <c r="V12" s="4">
         <v>64100002</v>
       </c>
-      <c r="S12" s="4">
+      <c r="W12" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="4">
         <v>10008</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="4">
-        <v>10008</v>
+      <c r="E13" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="F13" s="4">
         <v>10008</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="4">
+        <v>10008</v>
+      </c>
+      <c r="H13" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="H13" s="4">
+      <c r="I13" s="4">
         <v>10007</v>
       </c>
-      <c r="I13" s="4">
+      <c r="J13" s="4">
         <v>11</v>
       </c>
-      <c r="J13" s="4">
+      <c r="K13" s="4">
         <v>-1</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="L13" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="M13" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="N13" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="M13" s="4">
+      <c r="O13" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="P13" s="4">
         <v>2</v>
       </c>
-      <c r="N13" s="4">
-        <v>0</v>
-      </c>
-      <c r="O13" s="4">
-        <v>0</v>
-      </c>
-      <c r="P13" s="6" t="s">
+      <c r="Q13" s="4">
+        <v>0</v>
+      </c>
+      <c r="R13" s="4">
+        <v>0</v>
+      </c>
+      <c r="S13" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="Q13" s="4">
+      <c r="T13" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="U13" s="4">
         <v>4</v>
       </c>
-      <c r="R13" s="4">
+      <c r="V13" s="4">
         <v>64100003</v>
       </c>
-      <c r="S13" s="4">
+      <c r="W13" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="4">
         <v>10009</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="4">
-        <v>10009</v>
+      <c r="E14" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="F14" s="4">
         <v>10009</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="4">
+        <v>10009</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="H14" s="4">
+      <c r="I14" s="4">
         <v>10003</v>
       </c>
-      <c r="I14" s="4">
+      <c r="J14" s="4">
         <v>11</v>
       </c>
-      <c r="J14" s="4">
+      <c r="K14" s="4">
         <v>-1</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="L14" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="M14" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="N14" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="M14" s="4">
+      <c r="O14" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="P14" s="4">
         <v>2</v>
       </c>
-      <c r="N14" s="4">
-        <v>0</v>
-      </c>
-      <c r="O14" s="4">
-        <v>0</v>
-      </c>
-      <c r="P14" s="6" t="s">
+      <c r="Q14" s="4">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4">
+        <v>0</v>
+      </c>
+      <c r="S14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="T14" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="U14" s="4">
         <v>4</v>
       </c>
-      <c r="R14" s="4">
+      <c r="V14" s="4">
         <v>64100004</v>
       </c>
-      <c r="S14" s="4">
+      <c r="W14" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="4">
         <v>10010</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="4">
-        <v>10010</v>
+      <c r="E15" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="F15" s="4">
         <v>10010</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="4">
+        <v>10010</v>
+      </c>
+      <c r="H15" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="4">
+      <c r="I15" s="4">
         <v>10009</v>
       </c>
-      <c r="I15" s="4">
+      <c r="J15" s="4">
         <v>11</v>
       </c>
-      <c r="J15" s="4">
+      <c r="K15" s="4">
         <v>-1</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="L15" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="M15" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="N15" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="M15" s="4">
+      <c r="O15" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="P15" s="4">
         <v>2</v>
       </c>
-      <c r="N15" s="4">
-        <v>0</v>
-      </c>
-      <c r="O15" s="4">
-        <v>0</v>
-      </c>
-      <c r="P15" s="6" t="s">
+      <c r="Q15" s="4">
+        <v>0</v>
+      </c>
+      <c r="R15" s="4">
+        <v>0</v>
+      </c>
+      <c r="S15" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="T15" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="U15" s="4">
         <v>4</v>
       </c>
-      <c r="R15" s="4">
+      <c r="V15" s="4">
         <v>64100005</v>
       </c>
-      <c r="S15" s="4">
+      <c r="W15" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="4">
         <v>10011</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="4">
-        <v>10011</v>
+      <c r="E16" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="F16" s="4">
         <v>10011</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="4">
+        <v>10011</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="H16" s="4">
+      <c r="I16" s="4">
         <v>10011</v>
       </c>
-      <c r="I16" s="4">
+      <c r="J16" s="4">
         <v>40</v>
       </c>
-      <c r="J16" s="4">
+      <c r="K16" s="4">
         <v>-1</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="L16" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="M16" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="N16" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="M16" s="4">
+      <c r="O16" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="P16" s="4">
         <v>2</v>
       </c>
-      <c r="N16" s="4">
-        <v>0</v>
-      </c>
-      <c r="O16" s="4">
-        <v>0</v>
-      </c>
-      <c r="P16" s="6" t="s">
+      <c r="Q16" s="4">
+        <v>0</v>
+      </c>
+      <c r="R16" s="4">
+        <v>0</v>
+      </c>
+      <c r="S16" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="T16" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="U16" s="4">
         <v>4</v>
       </c>
-      <c r="R16" s="4">
+      <c r="V16" s="4">
         <v>64100006</v>
       </c>
-      <c r="S16" s="4">
+      <c r="W16" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="4">
         <v>10012</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="4">
-        <v>10012</v>
+      <c r="E17" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="F17" s="4">
         <v>10012</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="4">
+        <v>10012</v>
+      </c>
+      <c r="H17" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="H17" s="4">
+      <c r="I17" s="4">
         <v>10013</v>
       </c>
-      <c r="I17" s="4">
+      <c r="J17" s="4">
         <v>11</v>
       </c>
-      <c r="J17" s="4">
+      <c r="K17" s="4">
         <v>-1</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="L17" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="M17" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="N17" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="M17" s="4">
+      <c r="O17" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="P17" s="4">
         <v>2</v>
       </c>
-      <c r="N17" s="4">
-        <v>0</v>
-      </c>
-      <c r="O17" s="4">
-        <v>0</v>
-      </c>
-      <c r="P17" s="6" t="s">
+      <c r="Q17" s="4">
+        <v>0</v>
+      </c>
+      <c r="R17" s="4">
+        <v>0</v>
+      </c>
+      <c r="S17" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="T17" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="U17" s="4">
         <v>6</v>
       </c>
-      <c r="R17" s="4">
+      <c r="V17" s="4">
         <v>60400502</v>
       </c>
-      <c r="S17" s="4">
+      <c r="W17" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="4">
         <v>10013</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="4">
-        <v>10013</v>
+      <c r="E18" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="F18" s="4">
         <v>10013</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="4">
+        <v>10013</v>
+      </c>
+      <c r="H18" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="H18" s="4">
+      <c r="I18" s="4">
         <v>10014</v>
       </c>
-      <c r="I18" s="4">
+      <c r="J18" s="4">
         <v>9</v>
       </c>
-      <c r="J18" s="4">
+      <c r="K18" s="4">
         <v>-1</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="L18" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="M18" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="N18" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M18" s="4">
+      <c r="O18" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="P18" s="4">
         <v>2</v>
       </c>
-      <c r="N18" s="4">
-        <v>0</v>
-      </c>
-      <c r="O18" s="4">
-        <v>0</v>
-      </c>
-      <c r="P18" s="6" t="s">
+      <c r="Q18" s="4">
+        <v>0</v>
+      </c>
+      <c r="R18" s="4">
+        <v>0</v>
+      </c>
+      <c r="S18" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="Q18" s="4">
+      <c r="T18" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="U18" s="4">
         <v>7</v>
       </c>
-      <c r="R18" s="4">
+      <c r="V18" s="4">
         <v>1015</v>
       </c>
-      <c r="S18" s="4">
+      <c r="W18" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="4">
         <v>10014</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="4">
-        <v>10014</v>
+      <c r="E19" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="F19" s="4">
         <v>10014</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="4">
+        <v>10014</v>
+      </c>
+      <c r="H19" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="H19" s="4">
+      <c r="I19" s="4">
         <v>10015</v>
       </c>
-      <c r="I19" s="4">
+      <c r="J19" s="4">
         <v>10</v>
       </c>
-      <c r="J19" s="4">
+      <c r="K19" s="4">
         <v>-1</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="L19" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="L19" s="9" t="s">
+      <c r="M19" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="N19" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="M19" s="4">
+      <c r="O19" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="P19" s="4">
         <v>2</v>
       </c>
-      <c r="N19" s="4">
-        <v>0</v>
-      </c>
-      <c r="O19" s="4">
-        <v>0</v>
-      </c>
-      <c r="P19" s="6" t="s">
+      <c r="Q19" s="4">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="Q19" s="4">
+      <c r="T19" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="U19" s="4">
         <v>4</v>
       </c>
-      <c r="R19" s="4">
+      <c r="V19" s="4">
         <v>64100007</v>
       </c>
-      <c r="S19" s="4">
+      <c r="W19" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="4">
         <v>10015</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="4">
-        <v>10015</v>
+      <c r="E20" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="F20" s="4">
         <v>10015</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="4">
+        <v>10015</v>
+      </c>
+      <c r="H20" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="H20" s="4">
+      <c r="I20" s="4">
         <v>10015</v>
       </c>
-      <c r="I20" s="4">
+      <c r="J20" s="4">
         <v>10</v>
       </c>
-      <c r="J20" s="4">
+      <c r="K20" s="4">
         <v>-1</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="L20" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="M20" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="N20" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="M20" s="4">
+      <c r="O20" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="P20" s="4">
         <v>2</v>
       </c>
-      <c r="N20" s="4">
-        <v>0</v>
-      </c>
-      <c r="O20" s="4">
-        <v>0</v>
-      </c>
-      <c r="P20" s="6" t="s">
+      <c r="Q20" s="4">
+        <v>0</v>
+      </c>
+      <c r="R20" s="4">
+        <v>0</v>
+      </c>
+      <c r="S20" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="Q20" s="4">
+      <c r="T20" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="U20" s="4">
         <v>4</v>
       </c>
-      <c r="R20" s="4">
+      <c r="V20" s="4">
         <v>64100008</v>
       </c>
-      <c r="S20" s="4">
+      <c r="W20" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q22" s="7"/>
+    <row r="21" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="U22" s="7"/>
     </row>
-    <row r="23" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q23" s="7"/>
+    <row r="23" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="U23" s="7"/>
     </row>
-    <row r="24" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/JingLingConfig.xlsx
+++ b/Excel/JingLingConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E6C988-7231-4FBE-860A-14FAEE9E4E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A4BF60-FDC4-4078-AC5E-B460E0637C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JingLingProto" sheetId="1" r:id="rId1"/>
@@ -441,53 +441,16 @@
     <t>Lucky Star</t>
   </si>
   <si>
-    <t>Raccoon Spirit</t>
-  </si>
-  <si>
     <t>Greedy Turtle</t>
   </si>
   <si>
-    <t>Fish Spirit</t>
-  </si>
-  <si>
-    <t>Jaguar</t>
-  </si>
-  <si>
-    <t>Barbie Knot</t>
-  </si>
-  <si>
-    <t>Flame Magic</t>
-  </si>
-  <si>
-    <t>Alchemy Vitality Potion</t>
-  </si>
-  <si>
-    <t>Ghost</t>
-  </si>
-  <si>
-    <t>Naughty Spirit</t>
-  </si>
-  <si>
     <t>Bobo</t>
   </si>
   <si>
-    <t>Hua Hua</t>
-  </si>
-  <si>
-    <t>Dazed</t>
-  </si>
-  <si>
-    <t>The Pumpkin Villain</t>
-  </si>
-  <si>
     <t>Name_EN</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Bear Baby</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>ProDes_EN</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -600,6 +563,44 @@
   </si>
   <si>
     <t>GetDes_EN</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Raccoon Elf</t>
+  </si>
+  <si>
+    <t>Barbieko</t>
+  </si>
+  <si>
+    <t>Beary</t>
+  </si>
+  <si>
+    <t>Magic Flame</t>
+  </si>
+  <si>
+    <t>Bobby</t>
+  </si>
+  <si>
+    <t>Ghosty</t>
+  </si>
+  <si>
+    <t>Naughty Elf</t>
+  </si>
+  <si>
+    <t>Huahua</t>
+  </si>
+  <si>
+    <t>Daidai</t>
+  </si>
+  <si>
+    <t>Pumpkin Villain</t>
+  </si>
+  <si>
+    <t>Lantern Fish</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Money Leopard</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1057,13 +1058,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:W28"/>
+  <dimension ref="B1:W28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="15.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.375" style="2" customWidth="1"/>
     <col min="6" max="7" width="14.5" style="2" customWidth="1"/>
     <col min="8" max="8" width="23.625" style="2" customWidth="1"/>
     <col min="9" max="9" width="13.125" style="2" customWidth="1"/>
@@ -1078,25 +1080,25 @@
     <col min="24" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E2" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="W2" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1161,7 +1163,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1169,7 +1171,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>13</v>
@@ -1193,13 +1195,13 @@
         <v>52</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>20</v>
@@ -1214,7 +1216,7 @@
         <v>23</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="U4" s="5" t="s">
         <v>43</v>
@@ -1226,7 +1228,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>24</v>
       </c>
@@ -1291,7 +1293,8 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="3:23" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:23" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2"/>
       <c r="C6" s="4">
         <v>10001</v>
       </c>
@@ -1323,13 +1326,13 @@
         <v>61</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="N6" s="9" t="s">
         <v>65</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="P6" s="4">
         <v>2</v>
@@ -1344,7 +1347,7 @@
         <v>50</v>
       </c>
       <c r="T6" s="6" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="U6" s="4">
         <v>1</v>
@@ -1356,7 +1359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="4">
         <v>10002</v>
       </c>
@@ -1364,7 +1367,7 @@
         <v>28</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="F7" s="4">
         <v>10002</v>
@@ -1388,13 +1391,13 @@
         <v>53</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="N7" s="9" t="s">
         <v>66</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="P7" s="4">
         <v>2</v>
@@ -1409,7 +1412,7 @@
         <v>50</v>
       </c>
       <c r="T7" s="6" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="U7" s="4">
         <v>2</v>
@@ -1419,7 +1422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="4">
         <v>10003</v>
       </c>
@@ -1427,7 +1430,7 @@
         <v>30</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F8" s="4">
         <v>10003</v>
@@ -1451,13 +1454,13 @@
         <v>62</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="N8" s="9" t="s">
         <v>67</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="P8" s="4">
         <v>2</v>
@@ -1472,7 +1475,7 @@
         <v>48</v>
       </c>
       <c r="T8" s="6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="U8" s="4">
         <v>0</v>
@@ -1482,7 +1485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="4">
         <v>10004</v>
       </c>
@@ -1490,7 +1493,7 @@
         <v>31</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="F9" s="4">
         <v>10004</v>
@@ -1514,13 +1517,13 @@
         <v>54</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>77</v>
       </c>
       <c r="O9" s="9" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="P9" s="4">
         <v>2</v>
@@ -1535,7 +1538,7 @@
         <v>47</v>
       </c>
       <c r="T9" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="U9" s="4">
         <v>4</v>
@@ -1547,7 +1550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="4">
         <v>10005</v>
       </c>
@@ -1555,7 +1558,7 @@
         <v>32</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="F10" s="4">
         <v>10005</v>
@@ -1579,13 +1582,13 @@
         <v>55</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="N10" s="9" t="s">
         <v>68</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="P10" s="4">
         <v>2</v>
@@ -1600,7 +1603,7 @@
         <v>47</v>
       </c>
       <c r="T10" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="U10" s="4">
         <v>5</v>
@@ -1612,7 +1615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="4">
         <v>10006</v>
       </c>
@@ -1620,7 +1623,7 @@
         <v>33</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="F11" s="4">
         <v>10006</v>
@@ -1644,13 +1647,13 @@
         <v>95</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="N11" s="9" t="s">
         <v>94</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="P11" s="4">
         <v>2</v>
@@ -1665,7 +1668,7 @@
         <v>48</v>
       </c>
       <c r="T11" s="6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="U11" s="4">
         <v>7</v>
@@ -1677,7 +1680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="4">
         <v>10007</v>
       </c>
@@ -1685,7 +1688,7 @@
         <v>34</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="F12" s="4">
         <v>10007</v>
@@ -1709,13 +1712,13 @@
         <v>63</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="N12" s="9" t="s">
         <v>69</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="P12" s="4">
         <v>2</v>
@@ -1730,7 +1733,7 @@
         <v>47</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="U12" s="4">
         <v>4</v>
@@ -1742,7 +1745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="4">
         <v>10008</v>
       </c>
@@ -1750,7 +1753,7 @@
         <v>35</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="F13" s="4">
         <v>10008</v>
@@ -1774,13 +1777,13 @@
         <v>56</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="N13" s="9" t="s">
         <v>70</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="P13" s="4">
         <v>2</v>
@@ -1795,7 +1798,7 @@
         <v>47</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="U13" s="4">
         <v>4</v>
@@ -1807,7 +1810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="4">
         <v>10009</v>
       </c>
@@ -1815,7 +1818,7 @@
         <v>36</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="F14" s="4">
         <v>10009</v>
@@ -1839,13 +1842,13 @@
         <v>64</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="N14" s="9" t="s">
         <v>71</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="P14" s="4">
         <v>2</v>
@@ -1860,7 +1863,7 @@
         <v>49</v>
       </c>
       <c r="T14" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="U14" s="4">
         <v>4</v>
@@ -1872,7 +1875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="4">
         <v>10010</v>
       </c>
@@ -1880,7 +1883,7 @@
         <v>37</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="F15" s="4">
         <v>10010</v>
@@ -1904,13 +1907,13 @@
         <v>57</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>72</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="P15" s="4">
         <v>2</v>
@@ -1925,7 +1928,7 @@
         <v>47</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="U15" s="4">
         <v>4</v>
@@ -1937,7 +1940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="4">
         <v>10011</v>
       </c>
@@ -1945,7 +1948,7 @@
         <v>38</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="F16" s="4">
         <v>10011</v>
@@ -1969,13 +1972,13 @@
         <v>59</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="N16" s="9" t="s">
         <v>73</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="P16" s="4">
         <v>2</v>
@@ -1990,7 +1993,7 @@
         <v>47</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="U16" s="4">
         <v>4</v>
@@ -2010,7 +2013,7 @@
         <v>39</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F17" s="4">
         <v>10012</v>
@@ -2034,13 +2037,13 @@
         <v>58</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="N17" s="9" t="s">
         <v>74</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="P17" s="4">
         <v>2</v>
@@ -2055,7 +2058,7 @@
         <v>47</v>
       </c>
       <c r="T17" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="U17" s="4">
         <v>6</v>
@@ -2075,7 +2078,7 @@
         <v>40</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F18" s="4">
         <v>10013</v>
@@ -2099,13 +2102,13 @@
         <v>60</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="N18" s="9" t="s">
         <v>75</v>
       </c>
       <c r="O18" s="9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="P18" s="4">
         <v>2</v>
@@ -2120,7 +2123,7 @@
         <v>47</v>
       </c>
       <c r="T18" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="U18" s="4">
         <v>7</v>
@@ -2140,7 +2143,7 @@
         <v>41</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="F19" s="4">
         <v>10014</v>
@@ -2164,13 +2167,13 @@
         <v>63</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="N19" s="9" t="s">
         <v>76</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="P19" s="4">
         <v>2</v>
@@ -2185,7 +2188,7 @@
         <v>49</v>
       </c>
       <c r="T19" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="U19" s="4">
         <v>4</v>
@@ -2205,7 +2208,7 @@
         <v>42</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F20" s="4">
         <v>10015</v>
@@ -2229,13 +2232,13 @@
         <v>97</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="N20" s="9" t="s">
         <v>93</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="P20" s="4">
         <v>2</v>
@@ -2250,7 +2253,7 @@
         <v>48</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="U20" s="4">
         <v>4</v>

--- a/Excel/JingLingConfig.xlsx
+++ b/Excel/JingLingConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A4BF60-FDC4-4078-AC5E-B460E0637C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FF3D4C-FDAF-4328-8661-01201254EB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="161">
   <si>
     <t>Id</t>
   </si>
@@ -301,18 +301,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>重击概率+1%</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>闪避概率+1%</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>攻击提升100点</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>每天会随机给你一些金币！</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -368,9 +360,6 @@
     <t>100403;50</t>
   </si>
   <si>
-    <t>202103;0.01</t>
-  </si>
-  <si>
     <t>100202;0.01</t>
   </si>
   <si>
@@ -386,9 +375,6 @@
     <t>120703;100</t>
   </si>
   <si>
-    <t>100403;100</t>
-  </si>
-  <si>
     <t>100203;1000</t>
   </si>
   <si>
@@ -465,9 +451,6 @@
     <t>Life cap + 500 points</t>
   </si>
   <si>
-    <t>Critical Hit Rate + 1%</t>
-  </si>
-  <si>
     <t>Life cap + 1%</t>
   </si>
   <si>
@@ -483,9 +466,6 @@
     <t>Spell strength is increased by 100 points.</t>
   </si>
   <si>
-    <t>Attack +100</t>
-  </si>
-  <si>
     <t>Life limit + 1000 points</t>
   </si>
   <si>
@@ -601,6 +581,64 @@
   </si>
   <si>
     <t>Money Leopard</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨岩使者</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次玩家受到攻击伤害,有概率会在玩家附近释放一个击退技能,造成伤害</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>珍宝商店售卖</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sold at the Treasure Shop</t>
+  </si>
+  <si>
+    <t>Each time the player takes attack damage, there is a chance to trigger a knockback skill around them, dealing damage.</t>
+  </si>
+  <si>
+    <t>Giant Rock</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击提升300点</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack +300</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100403;300</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪避概率+2%</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>200303;0.02</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increased chance of evading attacks by 2%</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>重击概率+2%</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Critical Hit Rate + 2%</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>202103;0.02</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1083,19 +1121,19 @@
     <row r="1" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E2" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1160,7 +1198,7 @@
         <v>44</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1171,7 +1209,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>13</v>
@@ -1195,13 +1233,13 @@
         <v>52</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>20</v>
@@ -1216,7 +1254,7 @@
         <v>23</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="U4" s="5" t="s">
         <v>43</v>
@@ -1225,7 +1263,7 @@
         <v>45</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1290,7 +1328,7 @@
         <v>25</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="2:23" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1302,7 +1340,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F6" s="4">
         <v>10001</v>
@@ -1311,7 +1349,7 @@
         <v>10001</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I6" s="4">
         <v>10001</v>
@@ -1326,13 +1364,13 @@
         <v>61</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="P6" s="4">
         <v>2</v>
@@ -1347,7 +1385,7 @@
         <v>50</v>
       </c>
       <c r="T6" s="6" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="U6" s="4">
         <v>1</v>
@@ -1367,7 +1405,7 @@
         <v>28</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F7" s="4">
         <v>10002</v>
@@ -1391,13 +1429,13 @@
         <v>53</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="P7" s="4">
         <v>2</v>
@@ -1412,7 +1450,7 @@
         <v>50</v>
       </c>
       <c r="T7" s="6" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="U7" s="4">
         <v>2</v>
@@ -1430,7 +1468,7 @@
         <v>30</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F8" s="4">
         <v>10003</v>
@@ -1439,7 +1477,7 @@
         <v>10003</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="I8" s="4">
         <v>10008</v>
@@ -1451,16 +1489,16 @@
         <v>-1</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>62</v>
+        <v>158</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="P8" s="4">
         <v>2</v>
@@ -1475,7 +1513,7 @@
         <v>48</v>
       </c>
       <c r="T8" s="6" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="U8" s="4">
         <v>0</v>
@@ -1493,7 +1531,7 @@
         <v>31</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F9" s="4">
         <v>10004</v>
@@ -1502,7 +1540,7 @@
         <v>10004</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I9" s="4">
         <v>10004</v>
@@ -1517,13 +1555,13 @@
         <v>54</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O9" s="9" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="P9" s="4">
         <v>2</v>
@@ -1538,7 +1576,7 @@
         <v>47</v>
       </c>
       <c r="T9" s="6" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="U9" s="4">
         <v>4</v>
@@ -1558,7 +1596,7 @@
         <v>32</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="F10" s="4">
         <v>10005</v>
@@ -1567,7 +1605,7 @@
         <v>10005</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I10" s="4">
         <v>10016</v>
@@ -1582,13 +1620,13 @@
         <v>55</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P10" s="4">
         <v>2</v>
@@ -1603,7 +1641,7 @@
         <v>47</v>
       </c>
       <c r="T10" s="6" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="U10" s="4">
         <v>5</v>
@@ -1623,7 +1661,7 @@
         <v>33</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="F11" s="4">
         <v>10006</v>
@@ -1632,7 +1670,7 @@
         <v>10006</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I11" s="4">
         <v>10005</v>
@@ -1644,16 +1682,16 @@
         <v>-1</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="P11" s="4">
         <v>2</v>
@@ -1668,7 +1706,7 @@
         <v>48</v>
       </c>
       <c r="T11" s="6" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="U11" s="4">
         <v>7</v>
@@ -1688,7 +1726,7 @@
         <v>34</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F12" s="4">
         <v>10007</v>
@@ -1697,7 +1735,7 @@
         <v>10007</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="I12" s="4">
         <v>10006</v>
@@ -1709,16 +1747,16 @@
         <v>-1</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>63</v>
+        <v>155</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>111</v>
+        <v>157</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="P12" s="4">
         <v>2</v>
@@ -1733,7 +1771,7 @@
         <v>47</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="U12" s="4">
         <v>4</v>
@@ -1753,7 +1791,7 @@
         <v>35</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F13" s="4">
         <v>10008</v>
@@ -1762,7 +1800,7 @@
         <v>10008</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I13" s="4">
         <v>10007</v>
@@ -1777,13 +1815,13 @@
         <v>56</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="P13" s="4">
         <v>2</v>
@@ -1798,7 +1836,7 @@
         <v>47</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="U13" s="4">
         <v>4</v>
@@ -1818,7 +1856,7 @@
         <v>36</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F14" s="4">
         <v>10009</v>
@@ -1827,7 +1865,7 @@
         <v>10009</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>85</v>
+        <v>154</v>
       </c>
       <c r="I14" s="4">
         <v>10003</v>
@@ -1839,16 +1877,16 @@
         <v>-1</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="P14" s="4">
         <v>2</v>
@@ -1863,7 +1901,7 @@
         <v>49</v>
       </c>
       <c r="T14" s="6" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="U14" s="4">
         <v>4</v>
@@ -1883,7 +1921,7 @@
         <v>37</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="F15" s="4">
         <v>10010</v>
@@ -1892,7 +1930,7 @@
         <v>10010</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I15" s="4">
         <v>10009</v>
@@ -1907,13 +1945,13 @@
         <v>57</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="P15" s="4">
         <v>2</v>
@@ -1928,7 +1966,7 @@
         <v>47</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="U15" s="4">
         <v>4</v>
@@ -1948,7 +1986,7 @@
         <v>38</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F16" s="4">
         <v>10011</v>
@@ -1957,7 +1995,7 @@
         <v>10011</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="I16" s="4">
         <v>10011</v>
@@ -1972,13 +2010,13 @@
         <v>59</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="P16" s="4">
         <v>2</v>
@@ -1993,7 +2031,7 @@
         <v>47</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="U16" s="4">
         <v>4</v>
@@ -2013,7 +2051,7 @@
         <v>39</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F17" s="4">
         <v>10012</v>
@@ -2022,7 +2060,7 @@
         <v>10012</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I17" s="4">
         <v>10013</v>
@@ -2037,13 +2075,13 @@
         <v>58</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="P17" s="4">
         <v>2</v>
@@ -2058,7 +2096,7 @@
         <v>47</v>
       </c>
       <c r="T17" s="6" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="U17" s="4">
         <v>6</v>
@@ -2078,7 +2116,7 @@
         <v>40</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F18" s="4">
         <v>10013</v>
@@ -2087,7 +2125,7 @@
         <v>10013</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I18" s="4">
         <v>10014</v>
@@ -2102,13 +2140,13 @@
         <v>60</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O18" s="9" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="P18" s="4">
         <v>2</v>
@@ -2123,7 +2161,7 @@
         <v>47</v>
       </c>
       <c r="T18" s="6" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="U18" s="4">
         <v>7</v>
@@ -2143,7 +2181,7 @@
         <v>41</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F19" s="4">
         <v>10014</v>
@@ -2152,7 +2190,7 @@
         <v>10014</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I19" s="4">
         <v>10015</v>
@@ -2164,16 +2202,16 @@
         <v>-1</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="P19" s="4">
         <v>2</v>
@@ -2188,7 +2226,7 @@
         <v>49</v>
       </c>
       <c r="T19" s="6" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="U19" s="4">
         <v>4</v>
@@ -2208,7 +2246,7 @@
         <v>42</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F20" s="4">
         <v>10015</v>
@@ -2217,7 +2255,7 @@
         <v>10015</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I20" s="4">
         <v>10015</v>
@@ -2229,16 +2267,16 @@
         <v>-1</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="P20" s="4">
         <v>2</v>
@@ -2253,7 +2291,7 @@
         <v>48</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="U20" s="4">
         <v>4</v>
@@ -2265,7 +2303,71 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="4">
+        <v>10016</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F21" s="4">
+        <v>10016</v>
+      </c>
+      <c r="G21" s="4">
+        <v>10016</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I21" s="4">
+        <v>10015</v>
+      </c>
+      <c r="J21" s="4">
+        <v>10</v>
+      </c>
+      <c r="K21" s="4">
+        <v>-1</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="P21" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>0</v>
+      </c>
+      <c r="R21" s="4">
+        <v>0</v>
+      </c>
+      <c r="S21" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="T21" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="U21" s="4">
+        <v>4</v>
+      </c>
+      <c r="V21" s="4">
+        <v>64100015</v>
+      </c>
+      <c r="W21" s="4">
+        <v>0</v>
+      </c>
+    </row>
     <row r="22" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="U22" s="7"/>
     </row>

--- a/Excel/JingLingConfig.xlsx
+++ b/Excel/JingLingConfig.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FF3D4C-FDAF-4328-8661-01201254EB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557C4942-32FB-4C08-9F79-ED339137E791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JingLingProto" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
